--- a/products.xlsx
+++ b/products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\f3rna\OneDrive\Área de Trabalho\Meu site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70707FA5-9AA4-4988-AE9C-6F6ADB39ADB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB252531-1708-4394-A754-B33F7C6342C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,12 +16,11 @@
     <sheet name="Produtos" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="216">
   <si>
     <t>name</t>
   </si>
@@ -660,6 +659,15 @@
   </si>
   <si>
     <t>https://mercadolivre.com/sec/1sDhKG4</t>
+  </si>
+  <si>
+    <t>https://mercadolivre.com/sec/2TgLgP6</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_877493-MLA99478951284_112025-F.webp</t>
+  </si>
+  <si>
+    <t>Moedor Café Triturador Elétrico De Grãos Sementes Ervas Usb Cor Preto</t>
   </si>
 </sst>
 </file>
@@ -5300,52 +5308,63 @@
         <v>182</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" s="4"/>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B65" t="s">
+        <v>214</v>
+      </c>
+      <c r="C65" t="s">
+        <v>213</v>
+      </c>
+      <c r="D65" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="4"/>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="4"/>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="4"/>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="4"/>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="4"/>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="4"/>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="4"/>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="4"/>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="4"/>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="4"/>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="4"/>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="4"/>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="4"/>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="4"/>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="4"/>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">

--- a/products.xlsx
+++ b/products.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\f3rna\OneDrive\Área de Trabalho\Meu site\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.1.1\g\Meu site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB252531-1708-4394-A754-B33F7C6342C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0082018-CD79-484A-BE54-2A3FBDBCD959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="241">
   <si>
     <t>name</t>
   </si>
@@ -668,6 +668,81 @@
   </si>
   <si>
     <t>Moedor Café Triturador Elétrico De Grãos Sementes Ervas Usb Cor Preto</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_965103-MLA99575749404_122025-F.webp</t>
+  </si>
+  <si>
+    <t>https://mercadolivre.com/sec/27Z2Xa7</t>
+  </si>
+  <si>
+    <t>Chaleira Eletrica Atacama 1,8l - Unitermi</t>
+  </si>
+  <si>
+    <t>https://mercadolivre.com/sec/2LG9dWh</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_651826-MLA99986263335_112025-F.webp</t>
+  </si>
+  <si>
+    <t>Mixer Turbo Chef 3 Em 1 200w Triturador E Fuet Elgin</t>
+  </si>
+  <si>
+    <t>Filtro De Café Reutilizável Em Aço Inox Modelo 103 Peneira Permanente Sustentável Coar Café Tradicional Sem Papel Econômico E Durável Ponte Lar Utilidades</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_803581-MLA99564243074_122025-F.webp</t>
+  </si>
+  <si>
+    <t>https://mercadolivre.com/sec/2Qm1L72</t>
+  </si>
+  <si>
+    <t>Jogo Talheres Faqueiro Búzios Aço Inox 24 Peças Tramontina</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_885228-MLA105354697197_012026-F.webp</t>
+  </si>
+  <si>
+    <t>https://mercadolivre.com/sec/1VwwM4e</t>
+  </si>
+  <si>
+    <t>Drone Mini Pro Câmera 4k Com Gps 2 Baterias Completo Com Assistente De Pouso E Sensores De Obstáculos + Maleta De Transporte Drone Preto</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_974939-MLA99533870508_122025-F.webp</t>
+  </si>
+  <si>
+    <t>https://mercadolivre.com/sec/2perdnk</t>
+  </si>
+  <si>
+    <t>Smart Tv U8600f Crystal Uhd 4k 50 2025 Preto Samsung</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_673180-MLA99945056215_112025-F.webp</t>
+  </si>
+  <si>
+    <t>https://mercadolivre.com/sec/2JMTPE8</t>
+  </si>
+  <si>
+    <t>Tênis Masculino Feminino Kappa Park 2.0 Original</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_881886-MLB105747673925_012026-F-tnis-masculino-feminino-kappa-park-20-original.webp</t>
+  </si>
+  <si>
+    <t>https://mercadolivre.com/sec/2nnCew3</t>
+  </si>
+  <si>
+    <t>Console Playstation 5 Slim Edição Digital 825 Gb</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_677584-MLA99572203884_122025-F.webp</t>
+  </si>
+  <si>
+    <t>https://mercadolivre.com/sec/1it683k</t>
+  </si>
+  <si>
+    <t>Games</t>
   </si>
 </sst>
 </file>
@@ -1177,7 +1252,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
       <xdr:row>98</xdr:row>
-      <xdr:rowOff>166310</xdr:rowOff>
+      <xdr:rowOff>181429</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1720,7 +1795,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
       <xdr:row>98</xdr:row>
-      <xdr:rowOff>166310</xdr:rowOff>
+      <xdr:rowOff>181429</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2311,7 +2386,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
       <xdr:row>90</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:rowOff>9524</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2407,7 +2482,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
       <xdr:row>117</xdr:row>
-      <xdr:rowOff>38099</xdr:rowOff>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2455,7 +2530,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
       <xdr:row>142</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2949,7 +3024,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
       <xdr:row>90</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:rowOff>9524</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3045,7 +3120,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
       <xdr:row>117</xdr:row>
-      <xdr:rowOff>38099</xdr:rowOff>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3093,7 +3168,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
       <xdr:row>142</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3587,7 +3662,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
       <xdr:row>90</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:rowOff>9524</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3683,7 +3758,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
       <xdr:row>117</xdr:row>
-      <xdr:rowOff>38099</xdr:rowOff>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3731,7 +3806,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
       <xdr:row>142</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4099,6 +4174,150 @@
       <xdr:spPr bwMode="auto">
         <a:xfrm>
           <a:off x="10934700" y="11430000"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="32" name="AutoShape 1" descr="Chaleira Eletrica Atacama 1,8l - Unitermi">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7CE7DB6B-7B19-8680-1BF9-95A43506AB45}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="10934700" y="12382500"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="33" name="AutoShape 2" descr="Chaleira Eletrica Atacama 1,8l - Unitermi">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{20830922-E2A5-B1CD-0909-6796F50068B3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="10934700" y="12382500"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="34" name="AutoShape 3" descr="Smart Tv U8600f Crystal Uhd 4k 50 2025 Preto Samsung">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5598F972-184E-A2AD-231F-3D7D497575C7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="10934700" y="13335000"/>
           <a:ext cx="304800" cy="304800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5253,7 +5472,7 @@
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" s="6" t="s">
+      <c r="A61" t="s">
         <v>200</v>
       </c>
       <c r="B61" t="s">
@@ -5267,7 +5486,7 @@
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" s="6" t="s">
+      <c r="A62" t="s">
         <v>204</v>
       </c>
       <c r="B62" t="s">
@@ -5281,7 +5500,7 @@
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" s="4" t="s">
+      <c r="A63" t="s">
         <v>207</v>
       </c>
       <c r="B63" t="s">
@@ -5295,7 +5514,7 @@
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" s="5" t="s">
+      <c r="A64" t="s">
         <v>210</v>
       </c>
       <c r="B64" t="s">
@@ -5309,7 +5528,7 @@
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" s="4" t="s">
+      <c r="A65" t="s">
         <v>215</v>
       </c>
       <c r="B65" t="s">
@@ -5323,74 +5542,118 @@
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" s="4"/>
+      <c r="A66" t="s">
+        <v>218</v>
+      </c>
+      <c r="B66" t="s">
+        <v>216</v>
+      </c>
+      <c r="C66" t="s">
+        <v>217</v>
+      </c>
+      <c r="D66" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" s="4"/>
+      <c r="A67" t="s">
+        <v>221</v>
+      </c>
+      <c r="B67" t="s">
+        <v>220</v>
+      </c>
+      <c r="C67" t="s">
+        <v>219</v>
+      </c>
+      <c r="D67" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" s="4"/>
+      <c r="A68" t="s">
+        <v>222</v>
+      </c>
+      <c r="B68" t="s">
+        <v>223</v>
+      </c>
+      <c r="C68" t="s">
+        <v>224</v>
+      </c>
+      <c r="D68" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" s="4"/>
+      <c r="A69" t="s">
+        <v>225</v>
+      </c>
+      <c r="B69" t="s">
+        <v>226</v>
+      </c>
+      <c r="C69" t="s">
+        <v>227</v>
+      </c>
+      <c r="D69" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" s="4"/>
+      <c r="A70" t="s">
+        <v>228</v>
+      </c>
+      <c r="B70" t="s">
+        <v>229</v>
+      </c>
+      <c r="C70" t="s">
+        <v>230</v>
+      </c>
+      <c r="D70" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" s="4"/>
+      <c r="A71" t="s">
+        <v>231</v>
+      </c>
+      <c r="B71" t="s">
+        <v>232</v>
+      </c>
+      <c r="C71" t="s">
+        <v>233</v>
+      </c>
+      <c r="D71" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" s="4"/>
+      <c r="A72" t="s">
+        <v>234</v>
+      </c>
+      <c r="B72" t="s">
+        <v>235</v>
+      </c>
+      <c r="C72" t="s">
+        <v>236</v>
+      </c>
+      <c r="D72" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" s="4"/>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" s="4"/>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" s="4"/>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76" s="4"/>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A77" s="4"/>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" s="4"/>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A79" s="4"/>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80" s="4"/>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" s="4"/>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" s="4"/>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83" s="4"/>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A84" s="4"/>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A85" s="4"/>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A86" s="4"/>
-    </row>
-    <row r="87" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="4"/>
-    </row>
-    <row r="88" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="10"/>
-    </row>
+      <c r="A73" t="s">
+        <v>237</v>
+      </c>
+      <c r="B73" t="s">
+        <v>238</v>
+      </c>
+      <c r="C73" t="s">
+        <v>239</v>
+      </c>
+      <c r="D73" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="89" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="10"/>
     </row>

--- a/products.xlsx
+++ b/products.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.1.1\g\Meu site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0082018-CD79-484A-BE54-2A3FBDBCD959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B7C554E-7B44-4523-901A-B0010520092A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14580" yWindow="0" windowWidth="13995" windowHeight="15285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Produtos" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="274">
   <si>
     <t>name</t>
   </si>
@@ -743,6 +743,105 @@
   </si>
   <si>
     <t>Games</t>
+  </si>
+  <si>
+    <t>Aspirador de Pó Vertical e Portátil WAP High Speed Plus 1350W 3 em 1</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_887734-MLA99375017938_112025-F.webp</t>
+  </si>
+  <si>
+    <t>https://mercadolivre.com/sec/2kc1s8o</t>
+  </si>
+  <si>
+    <t>Purificador De Água Electrolux Pure4x Pe12 Cor Branco</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_681123-MLA99453121194_112025-F.webp</t>
+  </si>
+  <si>
+    <t>https://mercadolivre.com/sec/2gEDe3n</t>
+  </si>
+  <si>
+    <t>Graxa Lubrificante Para Correntes Chain Lub super Moto 200mL - Mobil</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_760097-MLA102137161656_122025-F.webp</t>
+  </si>
+  <si>
+    <t>https://mercadolivre.com/sec/127eqko</t>
+  </si>
+  <si>
+    <t>Comunicador Capacete V6 Plus 2 Unidades / Par Bluetooth 5.0</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_667088-MLB103999766319_012026-F-comunicador-capacete-v6-plus-2-unidades-par-bluetooth-50.webp</t>
+  </si>
+  <si>
+    <t>https://mercadolivre.com/sec/2nfue16</t>
+  </si>
+  <si>
+    <t>Válvula Para Caixa Dágua Duchão Blukit Com Dupla Retenção 5 m</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_992216-MLA99964861387_112025-F.webp</t>
+  </si>
+  <si>
+    <t>https://mercadolivre.com/sec/2Cs9ukY</t>
+  </si>
+  <si>
+    <t>Fechadura Eletronica Digital Com Biometria, Senha, Cartão Ic E Tuya App Bluetooth LAZORO</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_787439-MLA104930046625_012026-F.webp</t>
+  </si>
+  <si>
+    <t>https://mercadolivre.com/sec/28SnGN4</t>
+  </si>
+  <si>
+    <t>Máquina Fabricadora De Gelo 15kg Portátil Oninstek Cor Preto</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_907453-MLA92604606921_092025-F.webp</t>
+  </si>
+  <si>
+    <t>https://mercadolivre.com/sec/15mt72J</t>
+  </si>
+  <si>
+    <t>Bt-777239 Pipoqueira Elétrica Sem Óleo Máquina Fazer Pipoca Ar Quente 110v</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_757387-MLA99940407373_112025-F.webp</t>
+  </si>
+  <si>
+    <t>https://mercadolivre.com/sec/1uxHexs</t>
+  </si>
+  <si>
+    <t>Cooktop Indução Eletrico 2 Bocas Vidro Preto Trava Segurança</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_957403-MLA102883063095_122025-F.webp</t>
+  </si>
+  <si>
+    <t>https://mercadolivre.com/sec/1qw722k</t>
+  </si>
+  <si>
+    <t>Adaptador De Fogão De Indução Difusor Conversor Chapa Induçã Prateado</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_835336-MLB104060575249_012026-F.webp</t>
+  </si>
+  <si>
+    <t>https://mercadolivre.com/sec/2Gb3Zk1</t>
+  </si>
+  <si>
+    <t>Kit 5 Chumbinho Snyper Diabolô 5.5mm (promoção)</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_901992-MLA49833296518_052022-F.webp</t>
+  </si>
+  <si>
+    <t>https://mercadolivre.com/sec/1tNdLLT</t>
   </si>
 </sst>
 </file>
@@ -1149,21 +1248,21 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="1030" name="AutoShape 6" descr="Power Bank 20.000mah Haixia Carregador Rápido Com Display Portátil Branco">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F455CD0F-62D8-BF79-AB2C-08E96D7F216D}"/>
+        <xdr:cNvPr id="1031" name="AutoShape 7" descr="Power Bank 20.000mah Haixia Carregador Rápido Com Display Portátil Branco">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C4C78A62-28A1-DCE8-1C74-FF516CFAE812}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1173,104 +1272,8 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="0" y="9182100"/>
-          <a:ext cx="3905250" cy="4762500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1031" name="AutoShape 7" descr="Power Bank 20.000mah Haixia Carregador Rápido Com Display Portátil Branco">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C4C78A62-28A1-DCE8-1C74-FF516CFAE812}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
           <a:off x="0" y="13944600"/>
           <a:ext cx="419100" cy="419100"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>98</xdr:row>
-      <xdr:rowOff>181429</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1032" name="AutoShape 8" descr="Power Bank 20.000mah Haixia Carregador Rápido Com Display Portátil Branco">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0AE06157-08BA-65B7-7B7B-3FD2600A6657}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="0" y="14325600"/>
-          <a:ext cx="3905250" cy="4762500"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1788,54 +1791,6 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>98</xdr:row>
-      <xdr:rowOff>181429</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1044" name="AutoShape 20" descr="Power Bank 20.000mah Haixia Carregador Rápido Com Display Portátil Branco">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9CDB88F0-C995-549D-E034-90B82B50C608}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="0" y="14325600"/>
-          <a:ext cx="3905250" cy="4762500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
       <xdr:row>99</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
@@ -2338,7 +2293,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
       <xdr:row>87</xdr:row>
-      <xdr:rowOff>180974</xdr:rowOff>
+      <xdr:rowOff>171449</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2976,7 +2931,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
       <xdr:row>87</xdr:row>
-      <xdr:rowOff>180974</xdr:rowOff>
+      <xdr:rowOff>171449</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3614,7 +3569,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
       <xdr:row>87</xdr:row>
-      <xdr:rowOff>180974</xdr:rowOff>
+      <xdr:rowOff>171449</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -5653,29 +5608,183 @@
         <v>240</v>
       </c>
     </row>
-    <row r="88" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="89" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>241</v>
+      </c>
+      <c r="B74" t="s">
+        <v>242</v>
+      </c>
+      <c r="C74" t="s">
+        <v>243</v>
+      </c>
+      <c r="D74" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>244</v>
+      </c>
+      <c r="B75" t="s">
+        <v>245</v>
+      </c>
+      <c r="C75" t="s">
+        <v>246</v>
+      </c>
+      <c r="D75" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>247</v>
+      </c>
+      <c r="B76" t="s">
+        <v>248</v>
+      </c>
+      <c r="C76" t="s">
+        <v>249</v>
+      </c>
+      <c r="D76" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>250</v>
+      </c>
+      <c r="B77" t="s">
+        <v>251</v>
+      </c>
+      <c r="C77" t="s">
+        <v>252</v>
+      </c>
+      <c r="D77" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>253</v>
+      </c>
+      <c r="B78" t="s">
+        <v>254</v>
+      </c>
+      <c r="C78" t="s">
+        <v>255</v>
+      </c>
+      <c r="D78" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>256</v>
+      </c>
+      <c r="B79" t="s">
+        <v>257</v>
+      </c>
+      <c r="C79" t="s">
+        <v>258</v>
+      </c>
+      <c r="D79" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>259</v>
+      </c>
+      <c r="B80" t="s">
+        <v>260</v>
+      </c>
+      <c r="C80" t="s">
+        <v>261</v>
+      </c>
+      <c r="D80" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>262</v>
+      </c>
+      <c r="B81" t="s">
+        <v>263</v>
+      </c>
+      <c r="C81" t="s">
+        <v>264</v>
+      </c>
+      <c r="D81" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>265</v>
+      </c>
+      <c r="B82" t="s">
+        <v>266</v>
+      </c>
+      <c r="C82" t="s">
+        <v>267</v>
+      </c>
+      <c r="D82" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>268</v>
+      </c>
+      <c r="B83" t="s">
+        <v>269</v>
+      </c>
+      <c r="C83" t="s">
+        <v>270</v>
+      </c>
+      <c r="D83" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>271</v>
+      </c>
+      <c r="B84" t="s">
+        <v>272</v>
+      </c>
+      <c r="C84" t="s">
+        <v>273</v>
+      </c>
+      <c r="D84" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="89" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="10"/>
     </row>
-    <row r="90" spans="1:1" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A90" s="4"/>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="5"/>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="4"/>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="4"/>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="4"/>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="4"/>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="4"/>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">
@@ -6006,9 +6115,10 @@
     <hyperlink ref="B10" r:id="rId6" xr:uid="{5ED3D7ED-FC6D-4C44-8B5F-671739F6A728}"/>
     <hyperlink ref="B14" r:id="rId7" xr:uid="{AED35A75-AE1C-4AD0-9122-E943C0451F4B}"/>
     <hyperlink ref="A198" r:id="rId8" location="redirect=landing_international&amp;origin=vip" display="https://www.mercadolivre.com.br/importados/compra-internacional - redirect=landing_international&amp;origin=vip" xr:uid="{CC0DCAE0-A290-49ED-AC96-9E0C27938302}"/>
+    <hyperlink ref="B77" r:id="rId9" xr:uid="{C44C884A-2B1F-46D5-849E-2AEEA7727C26}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId9"/>
-  <drawing r:id="rId10"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId10"/>
+  <drawing r:id="rId11"/>
 </worksheet>
 </file>
--- a/products.xlsx
+++ b/products.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.1.1\g\Meu site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B7C554E-7B44-4523-901A-B0010520092A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D06F798D-5840-40DE-ADCB-70643202F74A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14580" yWindow="0" windowWidth="13995" windowHeight="15285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Produtos" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="271">
   <si>
     <t>name</t>
   </si>
@@ -37,9 +37,6 @@
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_744049-MLA99539379058_122025-F.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/1Fw8u2p</t>
-  </si>
-  <si>
     <t>Liquidificador Turbo Power Mondial 550W - L-99 FB</t>
   </si>
   <si>
@@ -49,9 +46,6 @@
     <t>https://http2.mlstatic.com/D_Q_NP_875816-MLA99972137443_112025-F.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/18T9Umx</t>
-  </si>
-  <si>
     <t>Eletrodoméstico</t>
   </si>
   <si>
@@ -61,9 +55,6 @@
     <t>https://http2.mlstatic.com/D_Q_NP_720182-MLA100247452907_122025-F.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/1b2MzfM</t>
-  </si>
-  <si>
     <t>Ventilador De Coluna Turbo 40cm Bronze Ventisol</t>
   </si>
   <si>
@@ -76,18 +67,12 @@
     <t>https://http2.mlstatic.com/D_Q_NP_902982-MLA88535253704_072025-F.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/2LkDmnS</t>
-  </si>
-  <si>
     <t>Parafusadeira Furadeira De Impacto The Black Tools Profissional TB-21PX 2 Baterias Com Maleta 60Hz Amarelo</t>
   </si>
   <si>
     <t>https://http2.mlstatic.com/D_Q_NP_865332-MLA96868279679_102025-F.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/2YQKQkb</t>
-  </si>
-  <si>
     <t>Ferramentas</t>
   </si>
   <si>
@@ -103,9 +88,6 @@
     <t>https://http2.mlstatic.com/D_Q_NP_801309-MLB89093855460_082025-F-xicara-copo-cafe-termico-inox-80ml-expresso-parede-dupla.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/2sTf5FK</t>
-  </si>
-  <si>
     <t>Canecas e copos térmicos</t>
   </si>
   <si>
@@ -121,9 +103,6 @@
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_860437-MLA99700923002_122025-F.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/2tbpYjv</t>
-  </si>
-  <si>
     <t>Ventilador</t>
   </si>
   <si>
@@ -139,9 +118,6 @@
     <t>https://http2.mlstatic.com/D_Q_NP_900674-MLA100087555981_122025-F.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/1TuEQG1</t>
-  </si>
-  <si>
     <t>Esporte</t>
   </si>
   <si>
@@ -151,45 +127,27 @@
     <t>https://http2.mlstatic.com/D_Q_NP_752031-MLA97933964606_112025-F.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/1ujuiTk</t>
-  </si>
-  <si>
     <t>Projetores</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/1sUGqAZ</t>
-  </si>
-  <si>
-    <t>https://mercadolivre.com/sec/1HbZVwu</t>
-  </si>
-  <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_709939-MLB89343355425_082025-F-kit-5-arandela-meia-lua-led-8w-8-fachos-ip66-bivolt-3000k.webp</t>
   </si>
   <si>
     <t>Kit 5 Arandela Meia Lua Led 8w 8 Fachos Ip66 Bivolt 3000k</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/2n4fJyb</t>
-  </si>
-  <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_860270-MLB82943676385_032025-F.webp</t>
   </si>
   <si>
     <t>Kit 2 Lâmpada Mata Mosquito Led Uv Pernilongo Frete Gratis 127/220v</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/1jytk4z</t>
-  </si>
-  <si>
     <t>Torneira Elétrica Digital Aço Escovado Cozinha Banheiro Aquecedor 3000w</t>
   </si>
   <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_695329-MLA99450348258_112025-F.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/2Si1QYg</t>
-  </si>
-  <si>
     <t>Casa</t>
   </si>
   <si>
@@ -199,9 +157,6 @@
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_867413-MLA99992012721_112025-F.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/1m8AhHT</t>
-  </si>
-  <si>
     <t>Lazer</t>
   </si>
   <si>
@@ -211,9 +166,6 @@
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_992444-MLA99468808790_112025-F.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/1CduD1g</t>
-  </si>
-  <si>
     <t>Eletronico</t>
   </si>
   <si>
@@ -223,27 +175,18 @@
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_795242-MLB97132720589_112025-F-800mlgarrafa-termica-agua-squeeze-inox-academiaquente-e-frio.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/2ngghju</t>
-  </si>
-  <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_790464-MLB103906889650_012026-F-copo-taca-2-em-1-termica-cocktail-glass-414ml-em-aco-inox.webp</t>
   </si>
   <si>
     <t>Copo Taça 2 Em 1 Térmica Cocktail Glass 414ml Em Aço Inox</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/28uVd1W</t>
-  </si>
-  <si>
     <t>Limpa Ar Condicionado Spray Orbi-air Carro Higienização</t>
   </si>
   <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_900675-MLB90291373988_082025-F-limpa-ar-condicionado-spray-orbi-air-carro-higienizaco.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/1vfErSU</t>
-  </si>
-  <si>
     <t>Automoveis</t>
   </si>
   <si>
@@ -253,9 +196,6 @@
     <t>Barbeador E Cortador De Cabelo 3 Em 1 Kemei Km-6558</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/2hnpu2j</t>
-  </si>
-  <si>
     <t>Saúde / Beleza</t>
   </si>
   <si>
@@ -265,27 +205,18 @@
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_868166-MLA90028576901_082025-F.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/13oiHwy</t>
-  </si>
-  <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_719702-MLB101390943178_122025-F-kit-conserto-remendo-furo-pneu-carro-moto-ferramenta-reparo.webp</t>
   </si>
   <si>
     <t>Kit Conserto Remendo Furo Pneu Carro Moto Ferramenta Reparo</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/2PUEXcM</t>
-  </si>
-  <si>
     <t>Picador Cortador De Legumes Médio Batata Tomate Frutas</t>
   </si>
   <si>
     <t>Headsets</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/1ZXR9DW</t>
-  </si>
-  <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_876544-MLA99513954036_112025-F.webp</t>
   </si>
   <si>
@@ -298,72 +229,45 @@
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_993004-MLA99910338111_112025-F.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/2Rc8HLf</t>
-  </si>
-  <si>
-    <t>https://mercadolivre.com/sec/2sUxuHc</t>
-  </si>
-  <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_979721-MLA79634440558_102024-F.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/1cizNHa</t>
-  </si>
-  <si>
     <t>Carregador Inteligente De Bateria Automotiva Carro Moto Caminhão Jet Sky Empilhadeira 12v 6 Amperes Bivolt 110/220 V - Thop Tech</t>
   </si>
   <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_941221-MLA99362401578_112025-F.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/24c28mv</t>
-  </si>
-  <si>
     <t>Kit De Internet Via Satelite Starlink Mini Branco</t>
   </si>
   <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_799612-MLA95359719699_102025-F.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/2FPWikU</t>
-  </si>
-  <si>
     <t>Creatina Monohidratada 1Kg Soldiers Nutrition 100% Pura Importada Alta Performance Músculo Treino</t>
   </si>
   <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_736821-MLA99962382095_112025-F.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/1jnwXVh</t>
-  </si>
-  <si>
     <t>Chuveiro Lorenzetti Loren Shower Eletrônico Branco 6800W</t>
   </si>
   <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_896908-MLA101388142032_122025-F.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/1tzvRRf</t>
-  </si>
-  <si>
     <t>Registro Regulador Gás Cozinha Botijão Domestico Com Visor</t>
   </si>
   <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_689702-MLB99978635776_122025-F.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/2R7dRad</t>
-  </si>
-  <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_671434-MLA99990718455_112025-F.webp</t>
   </si>
   <si>
     <t>Solução Nutritiva Hidroponia 1000L Plantpar Linha Flex Azul Vermelho</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/2wwantC</t>
-  </si>
-  <si>
     <t>Jardim</t>
   </si>
   <si>
@@ -379,30 +283,18 @@
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_738534-MLB99276147747_112025-F.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/2S8n7FA</t>
-  </si>
-  <si>
     <t>Espanta Mosca Ventilador Repelente De Mosquito Para Mesa</t>
   </si>
   <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_839239-MLA99452130470_112025-F.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/12HJFgJ</t>
-  </si>
-  <si>
-    <t>https://mercadolivre.com/sec/12FjkGn</t>
-  </si>
-  <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_654561-MLU74941455480_032024-F.webp</t>
   </si>
   <si>
     <t>Panquequeira E Crepioca Elétrica 3 Em 1 900w Britânia</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/25gezUF</t>
-  </si>
-  <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_844986-MLB90069025741_082025-F-maquina-de-crepe-crepeira-crepera-hotdog-linguica-queijo-110.webp</t>
   </si>
   <si>
@@ -415,24 +307,15 @@
     <t>Kit 2câmera Ip Icsee Prova D'água Infravermelho Externa Wifi - HW</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/1L5FG1o</t>
-  </si>
-  <si>
     <t>Kit Caneta Fine Line Cores Ponta Fina 0.4mm Cor Da Ti Tinta Kit 24 cores CORPO COLORIDO</t>
   </si>
   <si>
     <t>https://http2.mlstatic.com/D_Q_NP_890345-MLU77685731002_072024-R.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/1ZrfdzY</t>
-  </si>
-  <si>
     <t>Volta as aulas</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/2WN2mZg</t>
-  </si>
-  <si>
     <t>Lápis de Cor Multicolor 24 Cores 2B Para Desenho Modelo 11.2400N</t>
   </si>
   <si>
@@ -517,9 +400,6 @@
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_961028-MLU78230092907_082024-F.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/1Vco6Tq</t>
-  </si>
-  <si>
     <t>Bicicleta Ergométrica Bike Academia Spinning X11 cor preto e vermelho</t>
   </si>
   <si>
@@ -661,9 +541,6 @@
     <t>https://mercadolivre.com/sec/1sDhKG4</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/2TgLgP6</t>
-  </si>
-  <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_877493-MLA99478951284_112025-F.webp</t>
   </si>
   <si>
@@ -842,6 +719,120 @@
   </si>
   <si>
     <t>https://mercadolivre.com/sec/1tNdLLT</t>
+  </si>
+  <si>
+    <t>https://meli.la/21cXEcY</t>
+  </si>
+  <si>
+    <t>https://meli.la/2CPkNmk</t>
+  </si>
+  <si>
+    <t>https://meli.la/1y6fcNW</t>
+  </si>
+  <si>
+    <t>https://meli.la/1ZCKd41</t>
+  </si>
+  <si>
+    <t>https://meli.la/2Y7yAuu</t>
+  </si>
+  <si>
+    <t>https://meli.la/11V2esF</t>
+  </si>
+  <si>
+    <t>https://meli.la/1bEdwq6</t>
+  </si>
+  <si>
+    <t>https://meli.la/27CLU9a</t>
+  </si>
+  <si>
+    <t>https://meli.la/18dKknW</t>
+  </si>
+  <si>
+    <t>https://meli.la/19BZz5R</t>
+  </si>
+  <si>
+    <t>https://meli.la/1PXZbc3</t>
+  </si>
+  <si>
+    <t>https://meli.la/1btb7mZ</t>
+  </si>
+  <si>
+    <t>https://meli.la/11YMRyc</t>
+  </si>
+  <si>
+    <t>https://meli.la/11gEiZd</t>
+  </si>
+  <si>
+    <t>https://meli.la/2rZnJwR</t>
+  </si>
+  <si>
+    <t>https://meli.la/22ueKjd</t>
+  </si>
+  <si>
+    <t>https://meli.la/2dZDfGD</t>
+  </si>
+  <si>
+    <t>https://meli.la/1sSq3Yb</t>
+  </si>
+  <si>
+    <t>https://meli.la/2PvVt1v</t>
+  </si>
+  <si>
+    <t>https://meli.la/2hmw4vM</t>
+  </si>
+  <si>
+    <t>https://meli.la/1tj9PsH</t>
+  </si>
+  <si>
+    <t>https://meli.la/2vMQmuU</t>
+  </si>
+  <si>
+    <t>https://meli.la/2t2YYkG</t>
+  </si>
+  <si>
+    <t>https://meli.la/1Hvu5z8</t>
+  </si>
+  <si>
+    <t>https://meli.la/2WeFR34</t>
+  </si>
+  <si>
+    <t>https://meli.la/2esx5Kd</t>
+  </si>
+  <si>
+    <t>https://meli.la/2GEswZw</t>
+  </si>
+  <si>
+    <t>https://meli.la/2tKkeid</t>
+  </si>
+  <si>
+    <t>https://meli.la/1WvcnqX</t>
+  </si>
+  <si>
+    <t>https://meli.la/2J2CriG</t>
+  </si>
+  <si>
+    <t>https://meli.la/1QmhH6z</t>
+  </si>
+  <si>
+    <t>https://meli.la/1jpBfhb</t>
+  </si>
+  <si>
+    <t>https://meli.la/1BQmqfU</t>
+  </si>
+  <si>
+    <t>https://meli.la/25Kha96</t>
+  </si>
+  <si>
+    <t>https://meli.la/2nzvgYf</t>
+  </si>
+  <si>
+    <t>https://meli.la/18FZ6ki</t>
+  </si>
+  <si>
+    <t>https://meli.la/2fZRSnJ</t>
+  </si>
+  <si>
+    <t>https://meli.la/1sBEVL5</t>
   </si>
 </sst>
 </file>
@@ -4605,1161 +4596,1152 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>46</v>
+        <v>234</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>5</v>
+        <v>235</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D4" t="s">
         <v>8</v>
-      </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>237</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>238</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
         <v>23</v>
       </c>
-      <c r="B8" t="s">
-        <v>29</v>
-      </c>
       <c r="C8" s="2" t="s">
-        <v>93</v>
+        <v>239</v>
       </c>
       <c r="D8" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>240</v>
       </c>
       <c r="D9" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>241</v>
       </c>
       <c r="D10" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>163</v>
+        <v>124</v>
       </c>
       <c r="B11" t="s">
-        <v>164</v>
+        <v>125</v>
       </c>
       <c r="C11" t="s">
-        <v>165</v>
+        <v>242</v>
       </c>
       <c r="D11" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>243</v>
       </c>
       <c r="D12" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>45</v>
+        <v>244</v>
       </c>
       <c r="D13" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>39</v>
+        <v>245</v>
       </c>
       <c r="D14" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="B15" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>43</v>
+        <v>246</v>
       </c>
       <c r="D15" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>247</v>
       </c>
       <c r="D16" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="B17" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="C17" t="s">
-        <v>55</v>
+        <v>248</v>
       </c>
       <c r="D17" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="B18" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C18" t="s">
-        <v>59</v>
+        <v>249</v>
       </c>
       <c r="D18" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="B19" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C19" t="s">
-        <v>63</v>
+        <v>250</v>
       </c>
       <c r="D19" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="B20" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>67</v>
+        <v>251</v>
       </c>
       <c r="D20" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="B21" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="C21" t="s">
-        <v>70</v>
+        <v>252</v>
       </c>
       <c r="D21" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="B22" t="s">
-        <v>72</v>
-      </c>
-      <c r="C22" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="D22" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="B23" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="C23" t="s">
-        <v>77</v>
+        <v>253</v>
       </c>
       <c r="D23" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="B24" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C24" t="s">
-        <v>81</v>
+        <v>254</v>
       </c>
       <c r="D24" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="B25" t="s">
-        <v>82</v>
-      </c>
-      <c r="C25" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="D25" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="B26" t="s">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="C26" t="s">
-        <v>95</v>
+        <v>255</v>
       </c>
       <c r="D26" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>89</v>
+        <v>66</v>
       </c>
       <c r="B27" t="s">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="C27" t="s">
-        <v>87</v>
+        <v>256</v>
       </c>
       <c r="D27" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="B28" t="s">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="C28" t="s">
-        <v>92</v>
+        <v>257</v>
       </c>
       <c r="D28" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="B29" t="s">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="C29" t="s">
-        <v>98</v>
+        <v>258</v>
       </c>
       <c r="D29" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="B30" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="C30" t="s">
-        <v>101</v>
+        <v>259</v>
       </c>
       <c r="D30" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>102</v>
+        <v>74</v>
       </c>
       <c r="B31" t="s">
-        <v>103</v>
+        <v>75</v>
       </c>
       <c r="C31" t="s">
-        <v>104</v>
+        <v>260</v>
       </c>
       <c r="D31" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>105</v>
+        <v>76</v>
       </c>
       <c r="B32" t="s">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="C32" t="s">
-        <v>107</v>
+        <v>261</v>
       </c>
       <c r="D32" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="B33" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="C33" t="s">
-        <v>110</v>
+        <v>262</v>
       </c>
       <c r="D33" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="B34" t="s">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="C34" t="s">
-        <v>113</v>
+        <v>263</v>
       </c>
       <c r="D34" t="s">
-        <v>114</v>
+        <v>82</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>117</v>
+        <v>85</v>
       </c>
       <c r="B35" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="C35" t="s">
-        <v>119</v>
+        <v>264</v>
       </c>
       <c r="D35" t="s">
-        <v>114</v>
+        <v>82</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>120</v>
+        <v>87</v>
       </c>
       <c r="B36" t="s">
-        <v>121</v>
+        <v>88</v>
       </c>
       <c r="C36" t="s">
-        <v>122</v>
+        <v>265</v>
       </c>
       <c r="D36" t="s">
-        <v>114</v>
+        <v>82</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="B37" t="s">
-        <v>124</v>
+        <v>89</v>
       </c>
       <c r="C37" t="s">
-        <v>123</v>
+        <v>266</v>
       </c>
       <c r="D37" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>128</v>
+        <v>92</v>
       </c>
       <c r="B38" t="s">
-        <v>127</v>
+        <v>91</v>
       </c>
       <c r="C38" t="s">
-        <v>126</v>
+        <v>267</v>
       </c>
       <c r="D38" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>130</v>
+        <v>94</v>
       </c>
       <c r="B39" t="s">
-        <v>129</v>
+        <v>93</v>
       </c>
       <c r="C39" t="s">
-        <v>131</v>
+        <v>268</v>
       </c>
       <c r="D39" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>132</v>
+        <v>95</v>
       </c>
       <c r="B40" t="s">
-        <v>133</v>
+        <v>96</v>
       </c>
       <c r="C40" t="s">
-        <v>134</v>
+        <v>269</v>
       </c>
       <c r="D40" t="s">
-        <v>135</v>
+        <v>97</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="B41" t="s">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="C41" t="s">
-        <v>136</v>
+        <v>270</v>
       </c>
       <c r="D41" t="s">
-        <v>135</v>
+        <v>97</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="B42" t="s">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="C42" t="s">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="D42" t="s">
-        <v>135</v>
+        <v>97</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="B43" t="s">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="C43" t="s">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="D43" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="B44" t="s">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="C44" t="s">
-        <v>147</v>
+        <v>108</v>
       </c>
       <c r="D44" t="s">
-        <v>114</v>
+        <v>82</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>148</v>
+        <v>109</v>
       </c>
       <c r="B45" t="s">
-        <v>149</v>
+        <v>110</v>
       </c>
       <c r="C45" t="s">
-        <v>150</v>
+        <v>111</v>
       </c>
       <c r="D45" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>151</v>
+        <v>112</v>
       </c>
       <c r="B46" t="s">
-        <v>152</v>
+        <v>113</v>
       </c>
       <c r="C46" t="s">
-        <v>153</v>
+        <v>114</v>
       </c>
       <c r="D46" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>154</v>
+        <v>115</v>
       </c>
       <c r="B47" t="s">
-        <v>155</v>
+        <v>116</v>
       </c>
       <c r="C47" t="s">
-        <v>156</v>
+        <v>117</v>
       </c>
       <c r="D47" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>157</v>
+        <v>118</v>
       </c>
       <c r="B48" t="s">
-        <v>158</v>
+        <v>119</v>
       </c>
       <c r="C48" t="s">
-        <v>159</v>
+        <v>120</v>
       </c>
       <c r="D48" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>160</v>
+        <v>121</v>
       </c>
       <c r="B49" t="s">
-        <v>161</v>
+        <v>122</v>
       </c>
       <c r="C49" t="s">
-        <v>162</v>
+        <v>123</v>
       </c>
       <c r="D49" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>166</v>
+        <v>126</v>
       </c>
       <c r="B50" t="s">
-        <v>167</v>
+        <v>127</v>
       </c>
       <c r="C50" t="s">
-        <v>168</v>
+        <v>128</v>
       </c>
       <c r="D50" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>169</v>
+        <v>129</v>
       </c>
       <c r="B51" t="s">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="C51" t="s">
-        <v>171</v>
+        <v>131</v>
       </c>
       <c r="D51" t="s">
-        <v>114</v>
+        <v>82</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>172</v>
+        <v>132</v>
       </c>
       <c r="B52" t="s">
-        <v>173</v>
+        <v>133</v>
       </c>
       <c r="C52" t="s">
-        <v>174</v>
+        <v>134</v>
       </c>
       <c r="D52" t="s">
-        <v>175</v>
+        <v>135</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>178</v>
+        <v>138</v>
       </c>
       <c r="B53" t="s">
-        <v>177</v>
+        <v>137</v>
       </c>
       <c r="C53" t="s">
-        <v>176</v>
+        <v>136</v>
       </c>
       <c r="D53" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="B54" t="s">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="C54" t="s">
-        <v>181</v>
+        <v>141</v>
       </c>
       <c r="D54" t="s">
-        <v>182</v>
+        <v>142</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>184</v>
+        <v>144</v>
       </c>
       <c r="B55" t="s">
-        <v>183</v>
+        <v>143</v>
       </c>
       <c r="C55" t="s">
-        <v>185</v>
+        <v>145</v>
       </c>
       <c r="D55" t="s">
-        <v>175</v>
+        <v>135</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>186</v>
+        <v>146</v>
       </c>
       <c r="B56" t="s">
-        <v>187</v>
+        <v>147</v>
       </c>
       <c r="C56" t="s">
-        <v>188</v>
+        <v>148</v>
       </c>
       <c r="D56" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>189</v>
+        <v>149</v>
       </c>
       <c r="B57" t="s">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="C57" t="s">
-        <v>191</v>
+        <v>151</v>
       </c>
       <c r="D57" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>192</v>
+        <v>152</v>
       </c>
       <c r="B58" t="s">
-        <v>193</v>
+        <v>153</v>
       </c>
       <c r="C58" t="s">
-        <v>194</v>
+        <v>154</v>
       </c>
       <c r="D58" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>196</v>
+        <v>156</v>
       </c>
       <c r="B59" t="s">
-        <v>195</v>
+        <v>155</v>
       </c>
       <c r="D59" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>197</v>
+        <v>157</v>
       </c>
       <c r="B60" t="s">
-        <v>198</v>
+        <v>158</v>
       </c>
       <c r="C60" t="s">
-        <v>199</v>
+        <v>159</v>
       </c>
       <c r="D60" t="s">
-        <v>175</v>
+        <v>135</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="B61" t="s">
-        <v>201</v>
+        <v>161</v>
       </c>
       <c r="C61" t="s">
-        <v>202</v>
+        <v>162</v>
       </c>
       <c r="D61" t="s">
-        <v>203</v>
+        <v>163</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>204</v>
+        <v>164</v>
       </c>
       <c r="B62" t="s">
-        <v>205</v>
+        <v>165</v>
       </c>
       <c r="C62" t="s">
-        <v>206</v>
+        <v>166</v>
       </c>
       <c r="D62" t="s">
-        <v>203</v>
+        <v>163</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>207</v>
+        <v>167</v>
       </c>
       <c r="B63" t="s">
-        <v>208</v>
+        <v>168</v>
       </c>
       <c r="C63" t="s">
-        <v>209</v>
+        <v>169</v>
       </c>
       <c r="D63" t="s">
-        <v>203</v>
+        <v>163</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="B64" t="s">
-        <v>211</v>
+        <v>171</v>
       </c>
       <c r="C64" t="s">
-        <v>212</v>
+        <v>172</v>
       </c>
       <c r="D64" t="s">
-        <v>182</v>
+        <v>142</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>215</v>
+        <v>174</v>
       </c>
       <c r="B65" t="s">
-        <v>214</v>
+        <v>173</v>
       </c>
       <c r="C65" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="D65" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>218</v>
+        <v>177</v>
       </c>
       <c r="B66" t="s">
-        <v>216</v>
+        <v>175</v>
       </c>
       <c r="C66" t="s">
-        <v>217</v>
+        <v>176</v>
       </c>
       <c r="D66" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>221</v>
+        <v>180</v>
       </c>
       <c r="B67" t="s">
-        <v>220</v>
+        <v>179</v>
       </c>
       <c r="C67" t="s">
-        <v>219</v>
+        <v>178</v>
       </c>
       <c r="D67" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>222</v>
+        <v>181</v>
       </c>
       <c r="B68" t="s">
-        <v>223</v>
+        <v>182</v>
       </c>
       <c r="C68" t="s">
-        <v>224</v>
+        <v>183</v>
       </c>
       <c r="D68" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>225</v>
+        <v>184</v>
       </c>
       <c r="B69" t="s">
-        <v>226</v>
+        <v>185</v>
       </c>
       <c r="C69" t="s">
-        <v>227</v>
+        <v>186</v>
       </c>
       <c r="D69" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>228</v>
+        <v>187</v>
       </c>
       <c r="B70" t="s">
-        <v>229</v>
+        <v>188</v>
       </c>
       <c r="C70" t="s">
-        <v>230</v>
+        <v>189</v>
       </c>
       <c r="D70" t="s">
-        <v>175</v>
+        <v>135</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>231</v>
+        <v>190</v>
       </c>
       <c r="B71" t="s">
-        <v>232</v>
+        <v>191</v>
       </c>
       <c r="C71" t="s">
-        <v>233</v>
+        <v>192</v>
       </c>
       <c r="D71" t="s">
-        <v>175</v>
+        <v>135</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>234</v>
+        <v>193</v>
       </c>
       <c r="B72" t="s">
-        <v>235</v>
+        <v>194</v>
       </c>
       <c r="C72" t="s">
-        <v>236</v>
+        <v>195</v>
       </c>
       <c r="D72" t="s">
-        <v>182</v>
+        <v>142</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>237</v>
+        <v>196</v>
       </c>
       <c r="B73" t="s">
-        <v>238</v>
+        <v>197</v>
       </c>
       <c r="C73" t="s">
-        <v>239</v>
+        <v>198</v>
       </c>
       <c r="D73" t="s">
-        <v>240</v>
+        <v>199</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>241</v>
+        <v>200</v>
       </c>
       <c r="B74" t="s">
-        <v>242</v>
+        <v>201</v>
       </c>
       <c r="C74" t="s">
-        <v>243</v>
+        <v>202</v>
       </c>
       <c r="D74" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>244</v>
+        <v>203</v>
       </c>
       <c r="B75" t="s">
-        <v>245</v>
+        <v>204</v>
       </c>
       <c r="C75" t="s">
-        <v>246</v>
+        <v>205</v>
       </c>
       <c r="D75" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>247</v>
+        <v>206</v>
       </c>
       <c r="B76" t="s">
-        <v>248</v>
+        <v>207</v>
       </c>
       <c r="C76" t="s">
-        <v>249</v>
+        <v>208</v>
       </c>
       <c r="D76" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>250</v>
+        <v>209</v>
       </c>
       <c r="B77" t="s">
-        <v>251</v>
+        <v>210</v>
       </c>
       <c r="C77" t="s">
-        <v>252</v>
+        <v>211</v>
       </c>
       <c r="D77" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>253</v>
+        <v>212</v>
       </c>
       <c r="B78" t="s">
-        <v>254</v>
+        <v>213</v>
       </c>
       <c r="C78" t="s">
-        <v>255</v>
+        <v>214</v>
       </c>
       <c r="D78" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>256</v>
+        <v>215</v>
       </c>
       <c r="B79" t="s">
-        <v>257</v>
+        <v>216</v>
       </c>
       <c r="C79" t="s">
-        <v>258</v>
+        <v>217</v>
       </c>
       <c r="D79" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>259</v>
+        <v>218</v>
       </c>
       <c r="B80" t="s">
-        <v>260</v>
+        <v>219</v>
       </c>
       <c r="C80" t="s">
-        <v>261</v>
+        <v>220</v>
       </c>
       <c r="D80" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>262</v>
+        <v>221</v>
       </c>
       <c r="B81" t="s">
-        <v>263</v>
+        <v>222</v>
       </c>
       <c r="C81" t="s">
-        <v>264</v>
+        <v>223</v>
       </c>
       <c r="D81" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>265</v>
+        <v>224</v>
       </c>
       <c r="B82" t="s">
-        <v>266</v>
+        <v>225</v>
       </c>
       <c r="C82" t="s">
-        <v>267</v>
+        <v>226</v>
       </c>
       <c r="D82" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>268</v>
+        <v>227</v>
       </c>
       <c r="B83" t="s">
-        <v>269</v>
+        <v>228</v>
       </c>
       <c r="C83" t="s">
-        <v>270</v>
+        <v>229</v>
       </c>
       <c r="D83" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>271</v>
+        <v>230</v>
       </c>
       <c r="B84" t="s">
-        <v>272</v>
+        <v>231</v>
       </c>
       <c r="C84" t="s">
-        <v>273</v>
+        <v>232</v>
       </c>
       <c r="D84" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -6092,33 +6074,31 @@
     </row>
     <row r="198" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A198" s="8" t="s">
-        <v>115</v>
+        <v>83</v>
       </c>
     </row>
     <row r="199" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A199" s="9" t="s">
-        <v>116</v>
+        <v>84</v>
       </c>
     </row>
     <row r="200" spans="1:1" ht="21.75" x14ac:dyDescent="0.25">
       <c r="A200" s="11" t="s">
-        <v>117</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B3" r:id="rId1" xr:uid="{DCE316A2-6F5F-4239-8670-A2501AD068BA}"/>
-    <hyperlink ref="C3" r:id="rId2" xr:uid="{0D815271-BF44-4F66-9F26-67B6D283D73D}"/>
-    <hyperlink ref="B2" r:id="rId3" xr:uid="{E75C36C1-9EBF-4C4A-9D5E-6178C36287DA}"/>
-    <hyperlink ref="C2" r:id="rId4" xr:uid="{DBF9FFEB-73E8-453F-A3A0-B438C37C5A2B}"/>
-    <hyperlink ref="B9" r:id="rId5" xr:uid="{E7AF4AD0-FB67-4D18-A345-7AC735B2DDD9}"/>
-    <hyperlink ref="B10" r:id="rId6" xr:uid="{5ED3D7ED-FC6D-4C44-8B5F-671739F6A728}"/>
-    <hyperlink ref="B14" r:id="rId7" xr:uid="{AED35A75-AE1C-4AD0-9122-E943C0451F4B}"/>
-    <hyperlink ref="A198" r:id="rId8" location="redirect=landing_international&amp;origin=vip" display="https://www.mercadolivre.com.br/importados/compra-internacional - redirect=landing_international&amp;origin=vip" xr:uid="{CC0DCAE0-A290-49ED-AC96-9E0C27938302}"/>
-    <hyperlink ref="B77" r:id="rId9" xr:uid="{C44C884A-2B1F-46D5-849E-2AEEA7727C26}"/>
+    <hyperlink ref="B2" r:id="rId2" xr:uid="{E75C36C1-9EBF-4C4A-9D5E-6178C36287DA}"/>
+    <hyperlink ref="B9" r:id="rId3" xr:uid="{E7AF4AD0-FB67-4D18-A345-7AC735B2DDD9}"/>
+    <hyperlink ref="B10" r:id="rId4" xr:uid="{5ED3D7ED-FC6D-4C44-8B5F-671739F6A728}"/>
+    <hyperlink ref="B14" r:id="rId5" xr:uid="{AED35A75-AE1C-4AD0-9122-E943C0451F4B}"/>
+    <hyperlink ref="A198" r:id="rId6" location="redirect=landing_international&amp;origin=vip" display="https://www.mercadolivre.com.br/importados/compra-internacional - redirect=landing_international&amp;origin=vip" xr:uid="{CC0DCAE0-A290-49ED-AC96-9E0C27938302}"/>
+    <hyperlink ref="B77" r:id="rId7" xr:uid="{C44C884A-2B1F-46D5-849E-2AEEA7727C26}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId10"/>
-  <drawing r:id="rId11"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId8"/>
+  <drawing r:id="rId9"/>
 </worksheet>
 </file>
--- a/products.xlsx
+++ b/products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.1.1\g\Meu site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D06F798D-5840-40DE-ADCB-70643202F74A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B732659E-3639-464E-A743-F307B26F1FFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="269">
   <si>
     <t>name</t>
   </si>
@@ -328,72 +328,48 @@
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_613006-MLA101345266963_122025-F.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/1Rh8AZL</t>
-  </si>
-  <si>
     <t>Resistência Lorenzetti Acqua Ultra 220v 7800w Ref 3065b</t>
   </si>
   <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_808826-MLB79017709196_092024-F.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/2zZu6Sg</t>
-  </si>
-  <si>
     <t>Fio Nylon Aço 3mm Branco 35m Cinza Roçadeira Stihl Kawashima</t>
   </si>
   <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_636648-MLA99999816073_112025-F.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/1AenZWs</t>
-  </si>
-  <si>
     <t>Raquete Beach Tennis Carbono Camewin Cores Modelos + Estojo Cor Verde</t>
   </si>
   <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_986008-MLA99979982031_112025-F.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/2w2TJ7r</t>
-  </si>
-  <si>
     <t>Raquete Beach Tennis Shark Tour Modelo 2022</t>
   </si>
   <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_860626-MLA99986882345_112025-F.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/18UeUfu</t>
-  </si>
-  <si>
     <t>Conjunto Top Shorts Feminino Los Angeles Slim Moda Academia</t>
   </si>
   <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_982273-MLB79171128329_092024-F-conjunto-top-shorts-feminino-los-angeles-slim-moda-academia.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/2LYXLmr</t>
-  </si>
-  <si>
     <t>Kit Conjunto Fitness Feminino + Camiseta Roupa Academia Roxo Lisa M</t>
   </si>
   <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_841583-MLB89985983942_082025-F.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/2prGJrV</t>
-  </si>
-  <si>
     <t>Kit 5 Camisa Masculina Termica Academia Dry Fit Malha Fria</t>
   </si>
   <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_997360-MLB89836875348_082025-F-kit-5-camisa-masculina-termica-academia-dry-fit-malha-fria.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/25NhkpX</t>
-  </si>
-  <si>
     <t>Lâmpada Led Taschibra Bulbo 15w Branco Frio 6500k Luz Branco-frio</t>
   </si>
   <si>
@@ -403,36 +379,21 @@
     <t>Bicicleta Ergométrica Bike Academia Spinning X11 cor preto e vermelho</t>
   </si>
   <si>
-    <t>https://http2.mlstatic.com/D_Q_NP_936974-MLA99394285476_112025-R.webp</t>
-  </si>
-  <si>
-    <t>https://mercadolivre.com/sec/1mJZ2h8</t>
-  </si>
-  <si>
     <t>Conjunto De Mesa Com 4 Cadeiras + Guarda Sol Piscina Jardim</t>
   </si>
   <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_879619-MLB101681386902_122025-F-conjunto-de-mesa-com-4-cadeiras-guarda-sol-piscina-jardim.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/2La885p</t>
-  </si>
-  <si>
     <t>Smart Tag Compatível Find My Airtag Gps Rastreador Objetos Preto</t>
   </si>
   <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_806966-MLA105981916235_012026-F.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/2YMSL6L</t>
-  </si>
-  <si>
     <t>Eletronicos</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/1ZpQzt2</t>
-  </si>
-  <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_788270-MLB85613415884_062025-F-headphone-bluetooth-reduco-de-ruido-do-anc-com-microfone-f5.webp</t>
   </si>
   <si>
@@ -445,9 +406,6 @@
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_656171-MLB89388767014_082025-F-jaleco-avental-boto-feminino-oxford-com-punho-e-manga-longa.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/1TenQm8</t>
-  </si>
-  <si>
     <t>Roupas</t>
   </si>
   <si>
@@ -457,36 +415,24 @@
     <t>Roku Streaming Stick 2025 Para Tv Hd/fhd Controle Por Voz Preto De Voz</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/1aWvc2u</t>
-  </si>
-  <si>
     <t>Presente Natura Tododia Sabonetes em Barra Sortidos 5un 90G</t>
   </si>
   <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_776711-MLA92278973180_092025-F.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/22FSP1t</t>
-  </si>
-  <si>
     <t>Kit Moedor De Pés Automático Recarregável Usb Lixa De Pé</t>
   </si>
   <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_995783-MLB102098428340_122025-F-kit-moedor-de-pes-automatico-recarregavel-usb-lixa-de-pe.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/2qRexEz</t>
-  </si>
-  <si>
     <t>Quebra Sol Para Brisa Carro Protetor Solar Quebra Sol</t>
   </si>
   <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_998002-MLB90623040455_082025-F.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/2ieBGyx</t>
-  </si>
-  <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_796878-MLA88041903272_072025-F.webp</t>
   </si>
   <si>
@@ -499,18 +445,12 @@
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_626755-MLA105599427615_012026-F.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/2c5oeZX</t>
-  </si>
-  <si>
     <t>Nautica Voyage Edt 50ml Para Masculino</t>
   </si>
   <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_976778-MLA88319852853_072025-F.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/2Ajbyb7</t>
-  </si>
-  <si>
     <t>Cuidado Pessoais</t>
   </si>
   <si>
@@ -520,27 +460,18 @@
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_970885-MLA84177076022_052025-F.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/2orPX4n</t>
-  </si>
-  <si>
     <t>Perfume Natura Kaiak Extreme Deo colônia 100 ml</t>
   </si>
   <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_964055-MLA84536043026_052025-F.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/1Y8FsRZ</t>
-  </si>
-  <si>
     <t>Kit 10 Pares Meias Mash Invisível Esportiva Algodão Original</t>
   </si>
   <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_897046-MLB98663774114_112025-F-kit-10-pares-meias-mash-invisivel-esportiva-algodo-original.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/1sDhKG4</t>
-  </si>
-  <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_877493-MLA99478951284_112025-F.webp</t>
   </si>
   <si>
@@ -550,15 +481,9 @@
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_965103-MLA99575749404_122025-F.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/27Z2Xa7</t>
-  </si>
-  <si>
     <t>Chaleira Eletrica Atacama 1,8l - Unitermi</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/2LG9dWh</t>
-  </si>
-  <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_651826-MLA99986263335_112025-F.webp</t>
   </si>
   <si>
@@ -571,54 +496,36 @@
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_803581-MLA99564243074_122025-F.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/2Qm1L72</t>
-  </si>
-  <si>
     <t>Jogo Talheres Faqueiro Búzios Aço Inox 24 Peças Tramontina</t>
   </si>
   <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_885228-MLA105354697197_012026-F.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/1VwwM4e</t>
-  </si>
-  <si>
     <t>Drone Mini Pro Câmera 4k Com Gps 2 Baterias Completo Com Assistente De Pouso E Sensores De Obstáculos + Maleta De Transporte Drone Preto</t>
   </si>
   <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_974939-MLA99533870508_122025-F.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/2perdnk</t>
-  </si>
-  <si>
     <t>Smart Tv U8600f Crystal Uhd 4k 50 2025 Preto Samsung</t>
   </si>
   <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_673180-MLA99945056215_112025-F.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/2JMTPE8</t>
-  </si>
-  <si>
     <t>Tênis Masculino Feminino Kappa Park 2.0 Original</t>
   </si>
   <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_881886-MLB105747673925_012026-F-tnis-masculino-feminino-kappa-park-20-original.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/2nnCew3</t>
-  </si>
-  <si>
     <t>Console Playstation 5 Slim Edição Digital 825 Gb</t>
   </si>
   <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_677584-MLA99572203884_122025-F.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/1it683k</t>
-  </si>
-  <si>
     <t>Games</t>
   </si>
   <si>
@@ -628,99 +535,66 @@
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_887734-MLA99375017938_112025-F.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/2kc1s8o</t>
-  </si>
-  <si>
     <t>Purificador De Água Electrolux Pure4x Pe12 Cor Branco</t>
   </si>
   <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_681123-MLA99453121194_112025-F.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/2gEDe3n</t>
-  </si>
-  <si>
     <t>Graxa Lubrificante Para Correntes Chain Lub super Moto 200mL - Mobil</t>
   </si>
   <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_760097-MLA102137161656_122025-F.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/127eqko</t>
-  </si>
-  <si>
     <t>Comunicador Capacete V6 Plus 2 Unidades / Par Bluetooth 5.0</t>
   </si>
   <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_667088-MLB103999766319_012026-F-comunicador-capacete-v6-plus-2-unidades-par-bluetooth-50.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/2nfue16</t>
-  </si>
-  <si>
     <t>Válvula Para Caixa Dágua Duchão Blukit Com Dupla Retenção 5 m</t>
   </si>
   <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_992216-MLA99964861387_112025-F.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/2Cs9ukY</t>
-  </si>
-  <si>
     <t>Fechadura Eletronica Digital Com Biometria, Senha, Cartão Ic E Tuya App Bluetooth LAZORO</t>
   </si>
   <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_787439-MLA104930046625_012026-F.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/28SnGN4</t>
-  </si>
-  <si>
     <t>Máquina Fabricadora De Gelo 15kg Portátil Oninstek Cor Preto</t>
   </si>
   <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_907453-MLA92604606921_092025-F.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/15mt72J</t>
-  </si>
-  <si>
     <t>Bt-777239 Pipoqueira Elétrica Sem Óleo Máquina Fazer Pipoca Ar Quente 110v</t>
   </si>
   <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_757387-MLA99940407373_112025-F.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/1uxHexs</t>
-  </si>
-  <si>
     <t>Cooktop Indução Eletrico 2 Bocas Vidro Preto Trava Segurança</t>
   </si>
   <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_957403-MLA102883063095_122025-F.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/1qw722k</t>
-  </si>
-  <si>
     <t>Adaptador De Fogão De Indução Difusor Conversor Chapa Induçã Prateado</t>
   </si>
   <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_835336-MLB104060575249_012026-F.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/2Gb3Zk1</t>
-  </si>
-  <si>
     <t>Kit 5 Chumbinho Snyper Diabolô 5.5mm (promoção)</t>
   </si>
   <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_901992-MLA49833296518_052022-F.webp</t>
   </si>
   <si>
-    <t>https://mercadolivre.com/sec/1tNdLLT</t>
-  </si>
-  <si>
     <t>https://meli.la/21cXEcY</t>
   </si>
   <si>
@@ -833,6 +707,126 @@
   </si>
   <si>
     <t>https://meli.la/1sBEVL5</t>
+  </si>
+  <si>
+    <t>https://meli.la/2bvumfG</t>
+  </si>
+  <si>
+    <t>https://meli.la/2smh87H</t>
+  </si>
+  <si>
+    <t>https://meli.la/2DLpW5Q</t>
+  </si>
+  <si>
+    <t>https://meli.la/1EkqyuM</t>
+  </si>
+  <si>
+    <t>https://meli.la/1rD8F3M</t>
+  </si>
+  <si>
+    <t>https://meli.la/22T72GS</t>
+  </si>
+  <si>
+    <t>https://meli.la/1UEKC3s</t>
+  </si>
+  <si>
+    <t>https://meli.la/16r3ju1</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_936974-MLA99394285476_112025-F.webp</t>
+  </si>
+  <si>
+    <t>https://meli.la/1MYtETr</t>
+  </si>
+  <si>
+    <t>https://meli.la/19ddomp</t>
+  </si>
+  <si>
+    <t>https://meli.la/18ADTfp</t>
+  </si>
+  <si>
+    <t>https://meli.la/1GjXrYY</t>
+  </si>
+  <si>
+    <t>https://meli.la/1PR9G7q</t>
+  </si>
+  <si>
+    <t>https://meli.la/1weGFWB</t>
+  </si>
+  <si>
+    <t>https://meli.la/22gTvbC</t>
+  </si>
+  <si>
+    <t>https://meli.la/2oTrBuB</t>
+  </si>
+  <si>
+    <t>https://meli.la/2eGB3ZS</t>
+  </si>
+  <si>
+    <t>https://meli.la/28zwg9R</t>
+  </si>
+  <si>
+    <t>https://meli.la/1rwS7Wu</t>
+  </si>
+  <si>
+    <t>https://meli.la/2arH4rY</t>
+  </si>
+  <si>
+    <t>https://meli.la/1AfFvv9</t>
+  </si>
+  <si>
+    <t>https://meli.la/2mPjbiD</t>
+  </si>
+  <si>
+    <t>https://meli.la/2TKmFTZ</t>
+  </si>
+  <si>
+    <t>https://meli.la/1ZzCasp</t>
+  </si>
+  <si>
+    <t>https://meli.la/2EnnEaL</t>
+  </si>
+  <si>
+    <t>https://meli.la/1Vm89PB</t>
+  </si>
+  <si>
+    <t>https://meli.la/1o1SAyE</t>
+  </si>
+  <si>
+    <t>https://meli.la/2srmvpJ</t>
+  </si>
+  <si>
+    <t>https://meli.la/17DcsTC</t>
+  </si>
+  <si>
+    <t>https://meli.la/2n2mk5m</t>
+  </si>
+  <si>
+    <t>https://meli.la/2M4PEBk</t>
+  </si>
+  <si>
+    <t>https://meli.la/1kh7BDX</t>
+  </si>
+  <si>
+    <t>https://meli.la/2wsyKs6</t>
+  </si>
+  <si>
+    <t>https://meli.la/1RX25hU</t>
+  </si>
+  <si>
+    <t>https://meli.la/1pieq5F</t>
+  </si>
+  <si>
+    <t>https://meli.la/2nCX9ri</t>
+  </si>
+  <si>
+    <t>https://meli.la/2yucFU1</t>
+  </si>
+  <si>
+    <t>https://meli.la/1xz4tJF</t>
+  </si>
+  <si>
+    <t>https://meli.la/1Bqa2VC</t>
   </si>
 </sst>
 </file>
@@ -4602,7 +4596,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>234</v>
+        <v>192</v>
       </c>
       <c r="D2" t="s">
         <v>27</v>
@@ -4616,7 +4610,7 @@
         <v>4</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>235</v>
+        <v>193</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
@@ -4630,7 +4624,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>236</v>
+        <v>194</v>
       </c>
       <c r="D4" t="s">
         <v>8</v>
@@ -4644,7 +4638,7 @@
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>237</v>
+        <v>195</v>
       </c>
       <c r="D5" t="s">
         <v>8</v>
@@ -4669,7 +4663,7 @@
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>238</v>
+        <v>196</v>
       </c>
       <c r="D7" t="s">
         <v>17</v>
@@ -4683,7 +4677,7 @@
         <v>23</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>239</v>
+        <v>197</v>
       </c>
       <c r="D8" t="s">
         <v>19</v>
@@ -4697,7 +4691,7 @@
         <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>240</v>
+        <v>198</v>
       </c>
       <c r="D9" t="s">
         <v>22</v>
@@ -4711,7 +4705,7 @@
         <v>36</v>
       </c>
       <c r="C10" t="s">
-        <v>241</v>
+        <v>199</v>
       </c>
       <c r="D10" t="s">
         <v>24</v>
@@ -4719,13 +4713,13 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="B11" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="C11" t="s">
-        <v>242</v>
+        <v>200</v>
       </c>
       <c r="D11" t="s">
         <v>24</v>
@@ -4739,7 +4733,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>243</v>
+        <v>201</v>
       </c>
       <c r="D12" t="s">
         <v>27</v>
@@ -4753,7 +4747,7 @@
         <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>244</v>
+        <v>202</v>
       </c>
       <c r="D13" t="s">
         <v>19</v>
@@ -4767,7 +4761,7 @@
         <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>245</v>
+        <v>203</v>
       </c>
       <c r="D14" t="s">
         <v>32</v>
@@ -4781,7 +4775,7 @@
         <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>246</v>
+        <v>204</v>
       </c>
       <c r="D15" t="s">
         <v>35</v>
@@ -4795,7 +4789,7 @@
         <v>38</v>
       </c>
       <c r="C16" t="s">
-        <v>247</v>
+        <v>205</v>
       </c>
       <c r="D16" t="s">
         <v>24</v>
@@ -4809,7 +4803,7 @@
         <v>41</v>
       </c>
       <c r="C17" t="s">
-        <v>248</v>
+        <v>206</v>
       </c>
       <c r="D17" t="s">
         <v>42</v>
@@ -4823,7 +4817,7 @@
         <v>44</v>
       </c>
       <c r="C18" t="s">
-        <v>249</v>
+        <v>207</v>
       </c>
       <c r="D18" t="s">
         <v>45</v>
@@ -4837,7 +4831,7 @@
         <v>47</v>
       </c>
       <c r="C19" t="s">
-        <v>250</v>
+        <v>208</v>
       </c>
       <c r="D19" t="s">
         <v>48</v>
@@ -4851,7 +4845,7 @@
         <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>251</v>
+        <v>209</v>
       </c>
       <c r="D20" t="s">
         <v>22</v>
@@ -4865,7 +4859,7 @@
         <v>51</v>
       </c>
       <c r="C21" t="s">
-        <v>252</v>
+        <v>210</v>
       </c>
       <c r="D21" t="s">
         <v>22</v>
@@ -4890,7 +4884,7 @@
         <v>56</v>
       </c>
       <c r="C23" t="s">
-        <v>253</v>
+        <v>211</v>
       </c>
       <c r="D23" t="s">
         <v>58</v>
@@ -4904,7 +4898,7 @@
         <v>60</v>
       </c>
       <c r="C24" t="s">
-        <v>254</v>
+        <v>212</v>
       </c>
       <c r="D24" t="s">
         <v>58</v>
@@ -4929,7 +4923,7 @@
         <v>69</v>
       </c>
       <c r="C26" t="s">
-        <v>255</v>
+        <v>213</v>
       </c>
       <c r="D26" t="s">
         <v>42</v>
@@ -4943,7 +4937,7 @@
         <v>65</v>
       </c>
       <c r="C27" t="s">
-        <v>256</v>
+        <v>214</v>
       </c>
       <c r="D27" t="s">
         <v>8</v>
@@ -4957,7 +4951,7 @@
         <v>68</v>
       </c>
       <c r="C28" t="s">
-        <v>257</v>
+        <v>215</v>
       </c>
       <c r="D28" t="s">
         <v>8</v>
@@ -4971,7 +4965,7 @@
         <v>71</v>
       </c>
       <c r="C29" t="s">
-        <v>258</v>
+        <v>216</v>
       </c>
       <c r="D29" t="s">
         <v>55</v>
@@ -4985,7 +4979,7 @@
         <v>73</v>
       </c>
       <c r="C30" t="s">
-        <v>259</v>
+        <v>217</v>
       </c>
       <c r="D30" t="s">
         <v>45</v>
@@ -4999,7 +4993,7 @@
         <v>75</v>
       </c>
       <c r="C31" t="s">
-        <v>260</v>
+        <v>218</v>
       </c>
       <c r="D31" t="s">
         <v>58</v>
@@ -5013,7 +5007,7 @@
         <v>77</v>
       </c>
       <c r="C32" t="s">
-        <v>261</v>
+        <v>219</v>
       </c>
       <c r="D32" t="s">
         <v>42</v>
@@ -5027,7 +5021,7 @@
         <v>79</v>
       </c>
       <c r="C33" t="s">
-        <v>262</v>
+        <v>220</v>
       </c>
       <c r="D33" t="s">
         <v>42</v>
@@ -5041,7 +5035,7 @@
         <v>80</v>
       </c>
       <c r="C34" t="s">
-        <v>263</v>
+        <v>221</v>
       </c>
       <c r="D34" t="s">
         <v>82</v>
@@ -5055,7 +5049,7 @@
         <v>86</v>
       </c>
       <c r="C35" t="s">
-        <v>264</v>
+        <v>222</v>
       </c>
       <c r="D35" t="s">
         <v>82</v>
@@ -5069,7 +5063,7 @@
         <v>88</v>
       </c>
       <c r="C36" t="s">
-        <v>265</v>
+        <v>223</v>
       </c>
       <c r="D36" t="s">
         <v>82</v>
@@ -5083,7 +5077,7 @@
         <v>89</v>
       </c>
       <c r="C37" t="s">
-        <v>266</v>
+        <v>224</v>
       </c>
       <c r="D37" t="s">
         <v>8</v>
@@ -5097,7 +5091,7 @@
         <v>91</v>
       </c>
       <c r="C38" t="s">
-        <v>267</v>
+        <v>225</v>
       </c>
       <c r="D38" t="s">
         <v>8</v>
@@ -5111,7 +5105,7 @@
         <v>93</v>
       </c>
       <c r="C39" t="s">
-        <v>268</v>
+        <v>226</v>
       </c>
       <c r="D39" t="s">
         <v>42</v>
@@ -5125,7 +5119,7 @@
         <v>96</v>
       </c>
       <c r="C40" t="s">
-        <v>269</v>
+        <v>227</v>
       </c>
       <c r="D40" t="s">
         <v>97</v>
@@ -5139,7 +5133,7 @@
         <v>99</v>
       </c>
       <c r="C41" t="s">
-        <v>270</v>
+        <v>228</v>
       </c>
       <c r="D41" t="s">
         <v>97</v>
@@ -5153,7 +5147,7 @@
         <v>101</v>
       </c>
       <c r="C42" t="s">
-        <v>102</v>
+        <v>229</v>
       </c>
       <c r="D42" t="s">
         <v>97</v>
@@ -5161,13 +5155,13 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>102</v>
+      </c>
+      <c r="B43" t="s">
         <v>103</v>
       </c>
-      <c r="B43" t="s">
-        <v>104</v>
-      </c>
       <c r="C43" t="s">
-        <v>105</v>
+        <v>230</v>
       </c>
       <c r="D43" t="s">
         <v>42</v>
@@ -5175,13 +5169,13 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B44" t="s">
-        <v>107</v>
-      </c>
-      <c r="C44" t="s">
-        <v>108</v>
+        <v>105</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>231</v>
       </c>
       <c r="D44" t="s">
         <v>82</v>
@@ -5189,13 +5183,13 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B45" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C45" t="s">
-        <v>111</v>
+        <v>232</v>
       </c>
       <c r="D45" t="s">
         <v>32</v>
@@ -5203,13 +5197,13 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B46" t="s">
-        <v>113</v>
-      </c>
-      <c r="C46" t="s">
-        <v>114</v>
+        <v>109</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>233</v>
       </c>
       <c r="D46" t="s">
         <v>32</v>
@@ -5217,13 +5211,10 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B47" t="s">
-        <v>116</v>
-      </c>
-      <c r="C47" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="D47" t="s">
         <v>32</v>
@@ -5231,13 +5222,13 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="B48" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C48" t="s">
-        <v>120</v>
+        <v>234</v>
       </c>
       <c r="D48" t="s">
         <v>32</v>
@@ -5245,13 +5236,13 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="B49" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C49" t="s">
-        <v>123</v>
+        <v>235</v>
       </c>
       <c r="D49" t="s">
         <v>32</v>
@@ -5259,13 +5250,13 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="B50" t="s">
-        <v>127</v>
+        <v>237</v>
       </c>
       <c r="C50" t="s">
-        <v>128</v>
+        <v>236</v>
       </c>
       <c r="D50" t="s">
         <v>32</v>
@@ -5273,13 +5264,13 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="B51" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="C51" t="s">
-        <v>131</v>
+        <v>238</v>
       </c>
       <c r="D51" t="s">
         <v>82</v>
@@ -5287,27 +5278,27 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="B52" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="C52" t="s">
-        <v>134</v>
+        <v>239</v>
       </c>
       <c r="D52" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="B53" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="C53" t="s">
-        <v>136</v>
+        <v>240</v>
       </c>
       <c r="D53" t="s">
         <v>64</v>
@@ -5315,41 +5306,41 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="B54" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="C54" t="s">
-        <v>141</v>
+        <v>241</v>
       </c>
       <c r="D54" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="B55" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="C55" t="s">
-        <v>145</v>
+        <v>242</v>
       </c>
       <c r="D55" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="B56" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="C56" t="s">
-        <v>148</v>
+        <v>243</v>
       </c>
       <c r="D56" t="s">
         <v>58</v>
@@ -5357,13 +5348,10 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="B57" t="s">
-        <v>150</v>
-      </c>
-      <c r="C57" t="s">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="D57" t="s">
         <v>58</v>
@@ -5371,13 +5359,13 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="B58" t="s">
-        <v>153</v>
+        <v>136</v>
       </c>
       <c r="C58" t="s">
-        <v>154</v>
+        <v>244</v>
       </c>
       <c r="D58" t="s">
         <v>55</v>
@@ -5385,10 +5373,10 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="B59" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="D59" t="s">
         <v>8</v>
@@ -5396,83 +5384,83 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="B60" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="C60" t="s">
-        <v>159</v>
+        <v>245</v>
       </c>
       <c r="D60" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="B61" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
       <c r="C61" t="s">
-        <v>162</v>
+        <v>246</v>
       </c>
       <c r="D61" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="B62" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="C62" t="s">
-        <v>166</v>
+        <v>247</v>
       </c>
       <c r="D62" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="B63" t="s">
-        <v>168</v>
+        <v>147</v>
       </c>
       <c r="C63" t="s">
-        <v>169</v>
+        <v>248</v>
       </c>
       <c r="D63" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>170</v>
+        <v>148</v>
       </c>
       <c r="B64" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="C64" t="s">
-        <v>172</v>
+        <v>249</v>
       </c>
       <c r="D64" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>174</v>
+        <v>151</v>
       </c>
       <c r="B65" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="C65" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="D65" t="s">
         <v>42</v>
@@ -5480,13 +5468,13 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>177</v>
+        <v>153</v>
       </c>
       <c r="B66" t="s">
-        <v>175</v>
+        <v>152</v>
       </c>
       <c r="C66" t="s">
-        <v>176</v>
+        <v>250</v>
       </c>
       <c r="D66" t="s">
         <v>8</v>
@@ -5494,13 +5482,13 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>180</v>
+        <v>155</v>
       </c>
       <c r="B67" t="s">
-        <v>179</v>
+        <v>154</v>
       </c>
       <c r="C67" t="s">
-        <v>178</v>
+        <v>251</v>
       </c>
       <c r="D67" t="s">
         <v>8</v>
@@ -5508,13 +5496,13 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>181</v>
+        <v>156</v>
       </c>
       <c r="B68" t="s">
-        <v>182</v>
+        <v>157</v>
       </c>
       <c r="C68" t="s">
-        <v>183</v>
+        <v>252</v>
       </c>
       <c r="D68" t="s">
         <v>42</v>
@@ -5522,13 +5510,13 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
       <c r="B69" t="s">
-        <v>185</v>
+        <v>159</v>
       </c>
       <c r="C69" t="s">
-        <v>186</v>
+        <v>253</v>
       </c>
       <c r="D69" t="s">
         <v>42</v>
@@ -5536,69 +5524,69 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>187</v>
+        <v>160</v>
       </c>
       <c r="B70" t="s">
-        <v>188</v>
+        <v>161</v>
       </c>
       <c r="C70" t="s">
-        <v>189</v>
+        <v>254</v>
       </c>
       <c r="D70" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>190</v>
+        <v>162</v>
       </c>
       <c r="B71" t="s">
-        <v>191</v>
+        <v>163</v>
       </c>
       <c r="C71" t="s">
-        <v>192</v>
+        <v>255</v>
       </c>
       <c r="D71" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>193</v>
+        <v>164</v>
       </c>
       <c r="B72" t="s">
-        <v>194</v>
+        <v>165</v>
       </c>
       <c r="C72" t="s">
-        <v>195</v>
+        <v>256</v>
       </c>
       <c r="D72" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>196</v>
+        <v>166</v>
       </c>
       <c r="B73" t="s">
-        <v>197</v>
+        <v>167</v>
       </c>
       <c r="C73" t="s">
-        <v>198</v>
+        <v>257</v>
       </c>
       <c r="D73" t="s">
-        <v>199</v>
+        <v>168</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>200</v>
+        <v>169</v>
       </c>
       <c r="B74" t="s">
-        <v>201</v>
+        <v>170</v>
       </c>
       <c r="C74" t="s">
-        <v>202</v>
+        <v>258</v>
       </c>
       <c r="D74" t="s">
         <v>8</v>
@@ -5606,13 +5594,13 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="B75" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="C75" t="s">
-        <v>205</v>
+        <v>259</v>
       </c>
       <c r="D75" t="s">
         <v>42</v>
@@ -5620,13 +5608,13 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>206</v>
+        <v>173</v>
       </c>
       <c r="B76" t="s">
-        <v>207</v>
+        <v>174</v>
       </c>
       <c r="C76" t="s">
-        <v>208</v>
+        <v>260</v>
       </c>
       <c r="D76" t="s">
         <v>55</v>
@@ -5634,13 +5622,13 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>209</v>
+        <v>175</v>
       </c>
       <c r="B77" t="s">
-        <v>210</v>
+        <v>176</v>
       </c>
       <c r="C77" t="s">
-        <v>211</v>
+        <v>261</v>
       </c>
       <c r="D77" t="s">
         <v>55</v>
@@ -5648,13 +5636,13 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>212</v>
+        <v>177</v>
       </c>
       <c r="B78" t="s">
-        <v>213</v>
+        <v>178</v>
       </c>
       <c r="C78" t="s">
-        <v>214</v>
+        <v>262</v>
       </c>
       <c r="D78" t="s">
         <v>42</v>
@@ -5662,13 +5650,13 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>215</v>
+        <v>179</v>
       </c>
       <c r="B79" t="s">
-        <v>216</v>
+        <v>180</v>
       </c>
       <c r="C79" t="s">
-        <v>217</v>
+        <v>263</v>
       </c>
       <c r="D79" t="s">
         <v>42</v>
@@ -5676,13 +5664,13 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>218</v>
+        <v>181</v>
       </c>
       <c r="B80" t="s">
-        <v>219</v>
+        <v>182</v>
       </c>
       <c r="C80" t="s">
-        <v>220</v>
+        <v>264</v>
       </c>
       <c r="D80" t="s">
         <v>42</v>
@@ -5690,13 +5678,13 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>221</v>
+        <v>183</v>
       </c>
       <c r="B81" t="s">
-        <v>222</v>
+        <v>184</v>
       </c>
       <c r="C81" t="s">
-        <v>223</v>
+        <v>265</v>
       </c>
       <c r="D81" t="s">
         <v>8</v>
@@ -5704,13 +5692,13 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>224</v>
+        <v>185</v>
       </c>
       <c r="B82" t="s">
-        <v>225</v>
+        <v>186</v>
       </c>
       <c r="C82" t="s">
-        <v>226</v>
+        <v>266</v>
       </c>
       <c r="D82" t="s">
         <v>42</v>
@@ -5718,13 +5706,13 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>227</v>
+        <v>187</v>
       </c>
       <c r="B83" t="s">
-        <v>228</v>
+        <v>188</v>
       </c>
       <c r="C83" t="s">
-        <v>229</v>
+        <v>267</v>
       </c>
       <c r="D83" t="s">
         <v>42</v>
@@ -5732,13 +5720,13 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>230</v>
+        <v>189</v>
       </c>
       <c r="B84" t="s">
-        <v>231</v>
+        <v>190</v>
       </c>
       <c r="C84" t="s">
-        <v>232</v>
+        <v>268</v>
       </c>
       <c r="D84" t="s">
         <v>32</v>
@@ -6096,9 +6084,10 @@
     <hyperlink ref="B14" r:id="rId5" xr:uid="{AED35A75-AE1C-4AD0-9122-E943C0451F4B}"/>
     <hyperlink ref="A198" r:id="rId6" location="redirect=landing_international&amp;origin=vip" display="https://www.mercadolivre.com.br/importados/compra-internacional - redirect=landing_international&amp;origin=vip" xr:uid="{CC0DCAE0-A290-49ED-AC96-9E0C27938302}"/>
     <hyperlink ref="B77" r:id="rId7" xr:uid="{C44C884A-2B1F-46D5-849E-2AEEA7727C26}"/>
+    <hyperlink ref="C46" r:id="rId8" xr:uid="{D7CE1F55-B7E3-4E3A-87FB-E2DE297FF331}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId8"/>
-  <drawing r:id="rId9"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId9"/>
+  <drawing r:id="rId10"/>
 </worksheet>
 </file>
--- a/products.xlsx
+++ b/products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.1.1\g\Meu site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B732659E-3639-464E-A743-F307B26F1FFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A24DB082-9B32-4D9E-92E6-346E9ABB0DFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="276">
   <si>
     <t>name</t>
   </si>
@@ -827,6 +827,27 @@
   </si>
   <si>
     <t>https://meli.la/1Bqa2VC</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_910534-MLA99831868899_112025-F.webp</t>
+  </si>
+  <si>
+    <t>Escova de limpeza elétrica 12 em 1 giratória recarregável cabo regulável EPS-4112 - Branco</t>
+  </si>
+  <si>
+    <t>https://meli.la/1RhSueu</t>
+  </si>
+  <si>
+    <t>https://meli.la/1yztVbP</t>
+  </si>
+  <si>
+    <t>https://meli.la/1LEeuwY</t>
+  </si>
+  <si>
+    <t>https://meli.la/23SuRfp</t>
+  </si>
+  <si>
+    <t>https://meli.la/2ZZFc2P</t>
   </si>
 </sst>
 </file>
@@ -4872,6 +4893,9 @@
       <c r="B22" t="s">
         <v>54</v>
       </c>
+      <c r="C22" t="s">
+        <v>272</v>
+      </c>
       <c r="D22" t="s">
         <v>55</v>
       </c>
@@ -4911,6 +4935,9 @@
       <c r="B25" t="s">
         <v>61</v>
       </c>
+      <c r="C25" t="s">
+        <v>273</v>
+      </c>
       <c r="D25" t="s">
         <v>55</v>
       </c>
@@ -5216,6 +5243,9 @@
       <c r="B47" t="s">
         <v>111</v>
       </c>
+      <c r="C47" t="s">
+        <v>274</v>
+      </c>
       <c r="D47" t="s">
         <v>32</v>
       </c>
@@ -5353,6 +5383,9 @@
       <c r="B57" t="s">
         <v>134</v>
       </c>
+      <c r="C57" t="s">
+        <v>275</v>
+      </c>
       <c r="D57" t="s">
         <v>58</v>
       </c>
@@ -5730,6 +5763,20 @@
       </c>
       <c r="D84" t="s">
         <v>32</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>270</v>
+      </c>
+      <c r="B85" t="s">
+        <v>269</v>
+      </c>
+      <c r="C85" t="s">
+        <v>271</v>
+      </c>
+      <c r="D85" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
